--- a/Backlog_projeto_individual.xlsx
+++ b/Backlog_projeto_individual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15a7ca5f30cd3020/Desktop/Github-Projetos/Andrei/Projeto_Individual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{44FEAC60-A7DE-4F2C-869B-BD342CF57A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5959F067-A045-419A-9184-D18B9B7090B2}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{44FEAC60-A7DE-4F2C-869B-BD342CF57A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81882BF4-C7AD-4F76-8CDC-F58C94AD9E34}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="2160" windowWidth="17976" windowHeight="7332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
